--- a/research/traditional_assets/database/data/oman/oman_metals_mining.xlsx
+++ b/research/traditional_assets/database/data/oman/oman_metals_mining.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.08109999999999999</v>
+        <v>-0.0189</v>
       </c>
       <c r="G2">
-        <v>0.03903614457831325</v>
+        <v>-0.00448377581120944</v>
       </c>
       <c r="H2">
-        <v>0.03903614457831325</v>
+        <v>-0.00448377581120944</v>
       </c>
       <c r="I2">
-        <v>-0.02530120481927711</v>
+        <v>-0.1227138643067847</v>
       </c>
       <c r="J2">
-        <v>-0.02530120481927711</v>
+        <v>-0.1227138643067847</v>
       </c>
       <c r="K2">
-        <v>-4.45</v>
+        <v>-10.9</v>
       </c>
       <c r="L2">
-        <v>-0.0536144578313253</v>
+        <v>-0.1607669616519174</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.331</v>
+        <v>1.09</v>
       </c>
       <c r="V2">
-        <v>0.02829059829059829</v>
+        <v>0.1598240469208211</v>
       </c>
       <c r="W2">
-        <v>-0.2680722891566265</v>
+        <v>-0.6264367816091955</v>
       </c>
       <c r="X2">
-        <v>0.3779167386687614</v>
+        <v>0.9388765752920569</v>
       </c>
       <c r="Y2">
-        <v>-0.6459890278253879</v>
+        <v>-1.565313356901252</v>
       </c>
       <c r="Z2">
-        <v>1.215155774185992</v>
+        <v>0.9887850194694394</v>
       </c>
       <c r="AA2">
-        <v>-0.03074490513000703</v>
+        <v>-0.1213376307077542</v>
       </c>
       <c r="AB2">
-        <v>0.1073470426432952</v>
+        <v>0.1955687766164831</v>
       </c>
       <c r="AC2">
-        <v>-0.1380919477733022</v>
+        <v>-0.3169064073242373</v>
       </c>
       <c r="AD2">
-        <v>51.5</v>
+        <v>45.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>51.5</v>
+        <v>45.5</v>
       </c>
       <c r="AG2">
-        <v>51.169</v>
+        <v>44.41</v>
       </c>
       <c r="AH2">
-        <v>0.814873417721519</v>
+        <v>0.8696483180428135</v>
       </c>
       <c r="AI2">
-        <v>0.7474600870827285</v>
+        <v>0.8768548853343612</v>
       </c>
       <c r="AJ2">
-        <v>0.813898741828246</v>
+        <v>0.8668748780011711</v>
       </c>
       <c r="AK2">
-        <v>0.7462410127025333</v>
+        <v>0.8742125984251968</v>
       </c>
       <c r="AL2">
-        <v>3.6</v>
+        <v>3.27</v>
       </c>
       <c r="AM2">
-        <v>3.116</v>
+        <v>2.958</v>
       </c>
       <c r="AN2">
-        <v>26.41025641025641</v>
+        <v>-10.36446469248292</v>
       </c>
       <c r="AO2">
-        <v>-0.5833333333333334</v>
+        <v>-2.54434250764526</v>
       </c>
       <c r="AP2">
-        <v>26.24051282051282</v>
+        <v>-10.11617312072893</v>
       </c>
       <c r="AQ2">
-        <v>-0.6739409499358151</v>
+        <v>-2.812711291413117</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.08109999999999999</v>
+        <v>-0.0189</v>
       </c>
       <c r="G3">
-        <v>0.03903614457831325</v>
+        <v>-0.00448377581120944</v>
       </c>
       <c r="H3">
-        <v>0.03903614457831325</v>
+        <v>-0.00448377581120944</v>
       </c>
       <c r="I3">
-        <v>-0.02530120481927711</v>
+        <v>-0.1227138643067847</v>
       </c>
       <c r="J3">
-        <v>-0.02530120481927711</v>
+        <v>-0.1227138643067847</v>
       </c>
       <c r="K3">
-        <v>-4.45</v>
+        <v>-10.9</v>
       </c>
       <c r="L3">
-        <v>-0.0536144578313253</v>
+        <v>-0.1607669616519174</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.331</v>
+        <v>1.09</v>
       </c>
       <c r="V3">
-        <v>0.02829059829059829</v>
+        <v>0.1598240469208211</v>
       </c>
       <c r="W3">
-        <v>-0.2680722891566265</v>
+        <v>-0.6264367816091955</v>
       </c>
       <c r="X3">
-        <v>0.3779167386687614</v>
+        <v>0.9388765752920569</v>
       </c>
       <c r="Y3">
-        <v>-0.6459890278253879</v>
+        <v>-1.565313356901252</v>
       </c>
       <c r="Z3">
-        <v>1.215155774185992</v>
+        <v>0.9887850194694394</v>
       </c>
       <c r="AA3">
-        <v>-0.03074490513000703</v>
+        <v>-0.1213376307077542</v>
       </c>
       <c r="AB3">
-        <v>0.1073470426432952</v>
+        <v>0.1955687766164831</v>
       </c>
       <c r="AC3">
-        <v>-0.1380919477733022</v>
+        <v>-0.3169064073242373</v>
       </c>
       <c r="AD3">
-        <v>51.5</v>
+        <v>45.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>51.5</v>
+        <v>45.5</v>
       </c>
       <c r="AG3">
-        <v>51.169</v>
+        <v>44.41</v>
       </c>
       <c r="AH3">
-        <v>0.814873417721519</v>
+        <v>0.8696483180428135</v>
       </c>
       <c r="AI3">
-        <v>0.7474600870827285</v>
+        <v>0.8768548853343612</v>
       </c>
       <c r="AJ3">
-        <v>0.813898741828246</v>
+        <v>0.8668748780011711</v>
       </c>
       <c r="AK3">
-        <v>0.7462410127025333</v>
+        <v>0.8742125984251968</v>
       </c>
       <c r="AL3">
-        <v>3.6</v>
+        <v>3.27</v>
       </c>
       <c r="AM3">
-        <v>3.116</v>
+        <v>2.958</v>
       </c>
       <c r="AN3">
-        <v>26.41025641025641</v>
+        <v>-10.36446469248292</v>
       </c>
       <c r="AO3">
-        <v>-0.5833333333333334</v>
+        <v>-2.54434250764526</v>
       </c>
       <c r="AP3">
-        <v>26.24051282051282</v>
+        <v>-10.11617312072893</v>
       </c>
       <c r="AQ3">
-        <v>-0.6739409499358151</v>
+        <v>-2.812711291413117</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/oman/oman_metals_mining.xlsx
+++ b/research/traditional_assets/database/data/oman/oman_metals_mining.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0189</v>
+        <v>-0.0683</v>
       </c>
       <c r="G2">
-        <v>-0.00448377581120944</v>
+        <v>-0.0801762114537445</v>
       </c>
       <c r="H2">
-        <v>-0.00448377581120944</v>
+        <v>-0.0801762114537445</v>
       </c>
       <c r="I2">
-        <v>-0.1227138643067847</v>
+        <v>-0.09735682819383261</v>
       </c>
       <c r="J2">
-        <v>-0.1227138643067847</v>
+        <v>-0.09735682819383261</v>
       </c>
       <c r="K2">
-        <v>-10.9</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="L2">
-        <v>-0.1607669616519174</v>
+        <v>-0.1279001468428781</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="V2">
-        <v>0.1598240469208211</v>
+        <v>1.05</v>
       </c>
       <c r="W2">
-        <v>-0.6264367816091955</v>
+        <v>-1.363067292644758</v>
       </c>
       <c r="X2">
-        <v>0.9388765752920569</v>
+        <v>3.188726362792321</v>
       </c>
       <c r="Y2">
-        <v>-1.565313356901252</v>
+        <v>-4.551793655437079</v>
       </c>
       <c r="Z2">
-        <v>0.9887850194694394</v>
+        <v>1.340551181102362</v>
       </c>
       <c r="AA2">
-        <v>-0.1213376307077542</v>
+        <v>-0.1305118110236221</v>
       </c>
       <c r="AB2">
-        <v>0.1955687766164831</v>
+        <v>0.137401422752771</v>
       </c>
       <c r="AC2">
-        <v>-0.3169064073242373</v>
+        <v>-0.267913233776393</v>
       </c>
       <c r="AD2">
-        <v>45.5</v>
+        <v>44.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>45.5</v>
+        <v>44.4</v>
       </c>
       <c r="AG2">
-        <v>44.41</v>
+        <v>43.35</v>
       </c>
       <c r="AH2">
-        <v>0.8696483180428135</v>
+        <v>0.9779735682819384</v>
       </c>
       <c r="AI2">
-        <v>0.8768548853343612</v>
+        <v>1.055133079847909</v>
       </c>
       <c r="AJ2">
-        <v>0.8668748780011711</v>
+        <v>0.9774520856820744</v>
       </c>
       <c r="AK2">
-        <v>0.8742125984251968</v>
+        <v>1.056543992200829</v>
       </c>
       <c r="AL2">
-        <v>3.27</v>
+        <v>3.1</v>
       </c>
       <c r="AM2">
-        <v>2.958</v>
+        <v>3.1</v>
       </c>
       <c r="AN2">
-        <v>-10.36446469248292</v>
+        <v>-11.15577889447236</v>
       </c>
       <c r="AO2">
-        <v>-2.54434250764526</v>
+        <v>-2.138709677419355</v>
       </c>
       <c r="AP2">
-        <v>-10.11617312072893</v>
+        <v>-10.89195979899498</v>
       </c>
       <c r="AQ2">
-        <v>-2.812711291413117</v>
+        <v>-2.138709677419355</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0189</v>
+        <v>-0.0683</v>
       </c>
       <c r="G3">
-        <v>-0.00448377581120944</v>
+        <v>-0.0801762114537445</v>
       </c>
       <c r="H3">
-        <v>-0.00448377581120944</v>
+        <v>-0.0801762114537445</v>
       </c>
       <c r="I3">
-        <v>-0.1227138643067847</v>
+        <v>-0.09735682819383261</v>
       </c>
       <c r="J3">
-        <v>-0.1227138643067847</v>
+        <v>-0.09735682819383261</v>
       </c>
       <c r="K3">
-        <v>-10.9</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="L3">
-        <v>-0.1607669616519174</v>
+        <v>-0.1279001468428781</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="V3">
-        <v>0.1598240469208211</v>
+        <v>1.05</v>
       </c>
       <c r="W3">
-        <v>-0.6264367816091955</v>
+        <v>-1.363067292644758</v>
       </c>
       <c r="X3">
-        <v>0.9388765752920569</v>
+        <v>3.188726362792321</v>
       </c>
       <c r="Y3">
-        <v>-1.565313356901252</v>
+        <v>-4.551793655437079</v>
       </c>
       <c r="Z3">
-        <v>0.9887850194694394</v>
+        <v>1.340551181102362</v>
       </c>
       <c r="AA3">
-        <v>-0.1213376307077542</v>
+        <v>-0.1305118110236221</v>
       </c>
       <c r="AB3">
-        <v>0.1955687766164831</v>
+        <v>0.137401422752771</v>
       </c>
       <c r="AC3">
-        <v>-0.3169064073242373</v>
+        <v>-0.267913233776393</v>
       </c>
       <c r="AD3">
-        <v>45.5</v>
+        <v>44.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>45.5</v>
+        <v>44.4</v>
       </c>
       <c r="AG3">
-        <v>44.41</v>
+        <v>43.35</v>
       </c>
       <c r="AH3">
-        <v>0.8696483180428135</v>
+        <v>0.9779735682819384</v>
       </c>
       <c r="AI3">
-        <v>0.8768548853343612</v>
+        <v>1.055133079847909</v>
       </c>
       <c r="AJ3">
-        <v>0.8668748780011711</v>
+        <v>0.9774520856820744</v>
       </c>
       <c r="AK3">
-        <v>0.8742125984251968</v>
+        <v>1.056543992200829</v>
       </c>
       <c r="AL3">
-        <v>3.27</v>
+        <v>3.1</v>
       </c>
       <c r="AM3">
-        <v>2.958</v>
+        <v>3.1</v>
       </c>
       <c r="AN3">
-        <v>-10.36446469248292</v>
+        <v>-11.15577889447236</v>
       </c>
       <c r="AO3">
-        <v>-2.54434250764526</v>
+        <v>-2.138709677419355</v>
       </c>
       <c r="AP3">
-        <v>-10.11617312072893</v>
+        <v>-10.89195979899498</v>
       </c>
       <c r="AQ3">
-        <v>-2.812711291413117</v>
+        <v>-2.138709677419355</v>
       </c>
     </row>
   </sheetData>
